--- a/research/traditional_assets/database/data/serbia/serbia_air_transport.xlsx
+++ b/research/traditional_assets/database/data/serbia/serbia_air_transport.xlsx
@@ -588,115 +588,112 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.435</v>
+        <v>-0.423</v>
       </c>
       <c r="G2">
-        <v>-0.3786610878661088</v>
+        <v>0.2260692464358452</v>
       </c>
       <c r="H2">
-        <v>-0.3786610878661088</v>
+        <v>0.2260692464358452</v>
       </c>
       <c r="I2">
-        <v>-1.192468619246862</v>
+        <v>-0.6109979633401221</v>
       </c>
       <c r="J2">
-        <v>-1.192468619246862</v>
+        <v>-0.6109979633401221</v>
       </c>
       <c r="K2">
-        <v>-3.81</v>
+        <v>-0.921</v>
       </c>
       <c r="L2">
-        <v>-0.7970711297071129</v>
+        <v>-0.1875763747454175</v>
       </c>
       <c r="M2">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3.87997930677703e-05</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.003937007874015748</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>3.87997930677703e-05</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.003937007874015748</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>6.4</v>
+        <v>6.01</v>
       </c>
       <c r="V2">
-        <v>0.016554578375582</v>
+        <v>0.01182838024011021</v>
       </c>
       <c r="W2">
-        <v>-0.01310178817056396</v>
+        <v>-0.003246387028551287</v>
       </c>
       <c r="X2">
-        <v>0.08069840984874189</v>
+        <v>0.1241460726435817</v>
       </c>
       <c r="Y2">
-        <v>-0.09380019801930586</v>
+        <v>-0.127392459672133</v>
       </c>
       <c r="Z2">
-        <v>0.01692874344808046</v>
+        <v>0.01770645510277678</v>
       </c>
       <c r="AA2">
-        <v>-0.02018699532511687</v>
+        <v>-0.01081860800576992</v>
       </c>
       <c r="AB2">
-        <v>0.08069840984874189</v>
+        <v>0.1241116937419147</v>
       </c>
       <c r="AC2">
-        <v>-0.1008854051738588</v>
+        <v>-0.1349303017476846</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.332</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.332</v>
       </c>
       <c r="AG2">
-        <v>-6.4</v>
+        <v>-5.678</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.0006529880101960538</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.001383725388860177</v>
       </c>
       <c r="AJ2">
-        <v>-0.01683324566017885</v>
+        <v>-0.01130125671248472</v>
       </c>
       <c r="AK2">
-        <v>-0.02307969707897584</v>
+        <v>-0.02427304828105095</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.065</v>
+        <v>-0.053</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.2243243243243243</v>
       </c>
       <c r="AP2">
-        <v>-13.50210970464135</v>
+        <v>-3.836486486486486</v>
       </c>
       <c r="AQ2">
-        <v>87.69230769230769</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +713,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.435</v>
+        <v>-0.423</v>
       </c>
       <c r="G3">
-        <v>-0.3786610878661088</v>
+        <v>0.2260692464358452</v>
       </c>
       <c r="H3">
-        <v>-0.3786610878661088</v>
+        <v>0.2260692464358452</v>
       </c>
       <c r="I3">
-        <v>-1.192468619246862</v>
+        <v>-0.6109979633401221</v>
       </c>
       <c r="J3">
-        <v>-1.192468619246862</v>
+        <v>-0.6109979633401221</v>
       </c>
       <c r="K3">
-        <v>-3.81</v>
+        <v>-0.921</v>
       </c>
       <c r="L3">
-        <v>-0.7970711297071129</v>
+        <v>-0.1875763747454175</v>
       </c>
       <c r="M3">
-        <v>0.015</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>3.87997930677703e-05</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.003937007874015748</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.015</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>3.87997930677703e-05</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.003937007874015748</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>6.4</v>
+        <v>6.01</v>
       </c>
       <c r="V3">
-        <v>0.016554578375582</v>
+        <v>0.01182838024011021</v>
       </c>
       <c r="W3">
-        <v>-0.01310178817056396</v>
+        <v>-0.003246387028551287</v>
       </c>
       <c r="X3">
-        <v>0.08069840984874189</v>
+        <v>0.1241460726435817</v>
       </c>
       <c r="Y3">
-        <v>-0.09380019801930586</v>
+        <v>-0.127392459672133</v>
       </c>
       <c r="Z3">
-        <v>0.01692874344808046</v>
+        <v>0.01770645510277678</v>
       </c>
       <c r="AA3">
-        <v>-0.02018699532511687</v>
+        <v>-0.01081860800576992</v>
       </c>
       <c r="AB3">
-        <v>0.08069840984874189</v>
+        <v>0.1241116937419147</v>
       </c>
       <c r="AC3">
-        <v>-0.1008854051738588</v>
+        <v>-0.1349303017476846</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.332</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.332</v>
       </c>
       <c r="AG3">
-        <v>-6.4</v>
+        <v>-5.678</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.0006529880101960538</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.001383725388860177</v>
       </c>
       <c r="AJ3">
-        <v>-0.01683324566017885</v>
+        <v>-0.01130125671248472</v>
       </c>
       <c r="AK3">
-        <v>-0.02307969707897584</v>
+        <v>-0.02427304828105095</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.065</v>
+        <v>-0.053</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.2243243243243243</v>
       </c>
       <c r="AP3">
-        <v>-13.50210970464135</v>
+        <v>-3.836486486486486</v>
       </c>
       <c r="AQ3">
-        <v>87.69230769230769</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/serbia/serbia_air_transport.xlsx
+++ b/research/traditional_assets/database/data/serbia/serbia_air_transport.xlsx
@@ -588,25 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.423</v>
+        <v>-0.43</v>
+      </c>
+      <c r="E2">
+        <v>-0.6879999999999999</v>
       </c>
       <c r="G2">
-        <v>0.2260692464358452</v>
+        <v>0.3399280575539568</v>
       </c>
       <c r="H2">
-        <v>0.2260692464358452</v>
+        <v>0.3399280575539568</v>
       </c>
       <c r="I2">
-        <v>-0.6109979633401221</v>
+        <v>-0.6672661870503598</v>
       </c>
       <c r="J2">
-        <v>-0.6109979633401221</v>
+        <v>-0.3336330935251799</v>
       </c>
       <c r="K2">
-        <v>-0.921</v>
+        <v>0.09</v>
       </c>
       <c r="L2">
-        <v>-0.1875763747454175</v>
+        <v>0.01618705035971223</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +627,76 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.01</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="V2">
-        <v>0.01182838024011021</v>
+        <v>0.01449047369341024</v>
       </c>
       <c r="W2">
-        <v>-0.003246387028551287</v>
+        <v>0.0003756260434056761</v>
       </c>
       <c r="X2">
-        <v>0.1241460726435817</v>
+        <v>0.1111974351005173</v>
       </c>
       <c r="Y2">
-        <v>-0.127392459672133</v>
+        <v>-0.1108218090571117</v>
       </c>
       <c r="Z2">
-        <v>0.01770645510277678</v>
+        <v>0.02376860662956028</v>
       </c>
       <c r="AA2">
-        <v>-0.01081860800576992</v>
+        <v>-0.007929993758603295</v>
       </c>
       <c r="AB2">
-        <v>0.1241116937419147</v>
+        <v>0.1111870435389156</v>
       </c>
       <c r="AC2">
-        <v>-0.1349303017476846</v>
+        <v>-0.1191170372975189</v>
       </c>
       <c r="AD2">
-        <v>0.332</v>
+        <v>0.132</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.332</v>
+        <v>0.132</v>
       </c>
       <c r="AG2">
-        <v>-5.678</v>
+        <v>-8.157999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.0006529880101960538</v>
+        <v>0.0002306756700079688</v>
       </c>
       <c r="AI2">
-        <v>0.001383725388860177</v>
+        <v>0.0005105750932186345</v>
       </c>
       <c r="AJ2">
-        <v>-0.01130125671248472</v>
+        <v>-0.01446602664813048</v>
       </c>
       <c r="AK2">
-        <v>-0.02427304828105095</v>
+        <v>-0.03260044277139729</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.053</v>
+        <v>-0.181</v>
       </c>
       <c r="AN2">
-        <v>0.2243243243243243</v>
+        <v>0.07135135135135136</v>
       </c>
       <c r="AP2">
-        <v>-3.836486486486486</v>
+        <v>-4.40972972972973</v>
       </c>
       <c r="AQ2">
-        <v>56.60377358490566</v>
+        <v>20.49723756906078</v>
       </c>
     </row>
     <row r="3">
@@ -713,25 +716,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.423</v>
+        <v>-0.43</v>
+      </c>
+      <c r="E3">
+        <v>-0.6879999999999999</v>
       </c>
       <c r="G3">
-        <v>0.2260692464358452</v>
+        <v>0.3399280575539568</v>
       </c>
       <c r="H3">
-        <v>0.2260692464358452</v>
+        <v>0.3399280575539568</v>
       </c>
       <c r="I3">
-        <v>-0.6109979633401221</v>
+        <v>-0.6672661870503598</v>
       </c>
       <c r="J3">
-        <v>-0.6109979633401221</v>
+        <v>-0.3336330935251799</v>
       </c>
       <c r="K3">
-        <v>-0.921</v>
+        <v>0.09</v>
       </c>
       <c r="L3">
-        <v>-0.1875763747454175</v>
+        <v>0.01618705035971223</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,7 +746,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,76 +755,76 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.01</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="V3">
-        <v>0.01182838024011021</v>
+        <v>0.01449047369341024</v>
       </c>
       <c r="W3">
-        <v>-0.003246387028551287</v>
+        <v>0.0003756260434056761</v>
       </c>
       <c r="X3">
-        <v>0.1241460726435817</v>
+        <v>0.1111974351005173</v>
       </c>
       <c r="Y3">
-        <v>-0.127392459672133</v>
+        <v>-0.1108218090571117</v>
       </c>
       <c r="Z3">
-        <v>0.01770645510277678</v>
+        <v>0.02376860662956028</v>
       </c>
       <c r="AA3">
-        <v>-0.01081860800576992</v>
+        <v>-0.007929993758603295</v>
       </c>
       <c r="AB3">
-        <v>0.1241116937419147</v>
+        <v>0.1111870435389156</v>
       </c>
       <c r="AC3">
-        <v>-0.1349303017476846</v>
+        <v>-0.1191170372975189</v>
       </c>
       <c r="AD3">
-        <v>0.332</v>
+        <v>0.132</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.332</v>
+        <v>0.132</v>
       </c>
       <c r="AG3">
-        <v>-5.678</v>
+        <v>-8.157999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.0006529880101960538</v>
+        <v>0.0002306756700079688</v>
       </c>
       <c r="AI3">
-        <v>0.001383725388860177</v>
+        <v>0.0005105750932186345</v>
       </c>
       <c r="AJ3">
-        <v>-0.01130125671248472</v>
+        <v>-0.01446602664813048</v>
       </c>
       <c r="AK3">
-        <v>-0.02427304828105095</v>
+        <v>-0.03260044277139729</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.053</v>
+        <v>-0.181</v>
       </c>
       <c r="AN3">
-        <v>0.2243243243243243</v>
+        <v>0.07135135135135136</v>
       </c>
       <c r="AP3">
-        <v>-3.836486486486486</v>
+        <v>-4.40972972972973</v>
       </c>
       <c r="AQ3">
-        <v>56.60377358490566</v>
+        <v>20.49723756906078</v>
       </c>
     </row>
   </sheetData>
